--- a/Overview.xlsx
+++ b/Overview.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/RodWal-Capital-Insights/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{D60A6F84-4477-4005-8E6E-F694806FED89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5049C7D2-EFC6-4308-AA87-43993126BD80}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{D60A6F84-4477-4005-8E6E-F694806FED89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54E568E1-FB87-43A1-AA42-9EC4F282EBA2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{516D1755-2830-47A9-B007-CE0656FA4FE6}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Covariance" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">Portfolio!$K$12:$K$14</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">Portfolio!$M$12:$M$14</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="0" hidden="1">Portfolio!$K$10</definedName>
-    <definedName name="solver_lhs2" localSheetId="0" hidden="1">Portfolio!$K$12:$K$14</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">Portfolio!$M$10</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">Portfolio!$M$12:$M$14</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>Type</t>
   </si>
@@ -187,6 +187,12 @@
   </si>
   <si>
     <t>BNH</t>
+  </si>
+  <si>
+    <t>LOC CUR</t>
+  </si>
+  <si>
+    <t>FX</t>
   </si>
 </sst>
 </file>
@@ -349,10 +355,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -672,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAFB93E0-F994-4E59-B30E-6A296F0318C6}">
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -680,15 +682,17 @@
     <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" customWidth="1"/>
-    <col min="9" max="13" width="10.140625" customWidth="1"/>
-    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" customWidth="1"/>
+    <col min="8" max="8" width="8.140625" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="11" max="15" width="10.140625" customWidth="1"/>
+    <col min="16" max="16" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
@@ -699,133 +703,143 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="19" cm="1">
-        <f t="array" ref="B2">MMULT(TRANSPOSE(J12:J14),L12:L14)</f>
-        <v>8.9882410506205546E-2</v>
+        <f t="array" ref="B2">MMULT(TRANSPOSE(L12:L14),N12:N14)</f>
+        <v>9.5167749103224758E-2</v>
       </c>
       <c r="C2" s="19" cm="1">
-        <f t="array" ref="C2">MMULT(TRANSPOSE(K12:K14),L12:L14)</f>
-        <v>8.0750000000000002E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="array" ref="C2">MMULT(TRANSPOSE(M12:M14),N12:N14)</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="19">
-        <v>4.4999999999999998E-2</v>
+        <v>4.2500000000000003E-2</v>
       </c>
       <c r="C3" s="19">
-        <v>4.4999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+        <v>4.2500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="8">
         <f>(B2-B3)/B6</f>
-        <v>0.21192799233307164</v>
+        <v>0.2117349627819938</v>
       </c>
       <c r="C4" s="8">
         <f>(C2-C3)/C6</f>
-        <v>0.30741919289653646</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0.32907450547808315</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="19" cm="1">
-        <f t="array" ref="B5">MMULT(TRANSPOSE(J12:J14),MMULT(Covariance!B2:D4,Portfolio!J12:J14))</f>
-        <v>4.4851368562429564E-2</v>
+        <f t="array" ref="B5">MMULT(TRANSPOSE(L12:L14),MMULT(Covariance!B2:D4,Portfolio!L12:L14))</f>
+        <v>6.1873454232464722E-2</v>
       </c>
       <c r="C5" s="19" cm="1">
-        <f t="array" ref="C5">MMULT(TRANSPOSE(K12:K14),MMULT(Covariance!B2:D4,Portfolio!K12:K14))</f>
-        <v>1.3523532100000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="array" ref="C5">MMULT(TRANSPOSE(M12:M14),MMULT(Covariance!B2:D4,Portfolio!M12:M14))</f>
+        <v>1.2985960000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="19">
         <f>SQRT(B5)</f>
-        <v>0.21178141694310568</v>
+        <v>0.24874375214759611</v>
       </c>
       <c r="C6" s="19">
         <f>SQRT(C5)</f>
-        <v>0.11629072232985743</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+        <v>0.11395595640421786</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="8">
         <f>B2/B6</f>
-        <v>0.42441122457100255</v>
+        <v>0.38259352559237525</v>
       </c>
       <c r="C7" s="8">
         <f>C2/C6</f>
-        <v>0.69438041472434453</v>
+        <v>0.70202561168657751</v>
       </c>
       <c r="E7" s="12"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="E8" s="12"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F9" s="21" t="s">
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8">
+        <f>26.27*H10</f>
+        <v>73758.293123655909</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="H9" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
       <c r="I9" s="21"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="3">
-        <f>SUBTOTAL(9,F12:F17)</f>
-        <v>2602.1583783783785</v>
-      </c>
-      <c r="G10" s="3">
-        <f t="shared" ref="G10:H10" si="0">SUBTOTAL(9,G12:G17)</f>
-        <v>2924.0035135135131</v>
-      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
       <c r="H10" s="3">
+        <f>SUBTOTAL(9,H12:H17)</f>
+        <v>2807.7005376344086</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" ref="I10:J10" si="0">SUBTOTAL(9,I12:I17)</f>
+        <v>3238.7005376344086</v>
+      </c>
+      <c r="J10" s="3">
         <f t="shared" si="0"/>
-        <v>321.84513513513497</v>
-      </c>
-      <c r="I10" s="4">
-        <f t="shared" ref="I10" si="1">H10/F10</f>
-        <v>0.12368391478757855</v>
-      </c>
-      <c r="J10" s="4">
-        <f>SUM(J12:J14)</f>
+        <v>431</v>
+      </c>
+      <c r="K10" s="4">
+        <f t="shared" ref="K10" si="1">J10/H10</f>
+        <v>0.15350639935522947</v>
+      </c>
+      <c r="L10" s="4">
+        <f>SUM(L12:L14)</f>
         <v>1</v>
       </c>
-      <c r="K10" s="4">
-        <f>SUM(K12:K14)</f>
+      <c r="M10" s="4">
+        <f>SUM(M12:M14)</f>
         <v>1</v>
       </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-    </row>
-    <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+    </row>
+    <row r="11" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="18" t="s">
         <v>0</v>
       </c>
@@ -833,72 +847,78 @@
         <v>1</v>
       </c>
       <c r="F11" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="I11" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="J11" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="K11" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="L11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="20" t="s">
+      <c r="M11" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="20" t="s">
+      <c r="N11" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M11" s="20" t="s">
+      <c r="O11" s="20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D12" s="15" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="1">
-        <f>(4992.71+4994.72)/18.5</f>
-        <v>539.86108108108112</v>
-      </c>
-      <c r="G12" s="1">
-        <f>F12+H12</f>
-        <v>553.75621621621622</v>
-      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
       <c r="H12" s="1">
-        <f>(134.29+122.77)/18.5</f>
-        <v>13.895135135135135</v>
-      </c>
-      <c r="I12" s="4">
-        <f>IFERROR(H12/F12,0)</f>
-        <v>2.5738353109859089E-2</v>
-      </c>
-      <c r="J12" s="4">
-        <f>F12/$F$10</f>
-        <v>0.2074666498268693</v>
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" ref="J12" si="2">I12-H12</f>
+        <v>0</v>
       </c>
       <c r="K12" s="4">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
+        <f>IFERROR(J12/H12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <f>H12/$H$10</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="4">
+        <v>0</v>
+      </c>
+      <c r="N12" s="12">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="M12" s="12">
+      <c r="O12" s="12">
         <v>0.08</v>
       </c>
-      <c r="P12" s="6"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="10"/>
-      <c r="U12" s="9"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="R12" s="6"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="10"/>
+      <c r="W12" s="9"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D13" s="15" t="s">
         <v>25</v>
       </c>
@@ -906,181 +926,190 @@
         <v>3</v>
       </c>
       <c r="F13" s="1">
-        <f>5500/18.5</f>
-        <v>297.29729729729729</v>
+        <v>10094.23</v>
       </c>
       <c r="G13" s="1">
-        <v>297.29729729729729</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="H13" s="1">
-        <f t="shared" ref="H13" si="2">G13-F13</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="4">
-        <f t="shared" ref="I13:I16" si="3">IFERROR(H13/F13,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="4">
-        <f t="shared" ref="J13:J14" si="4">F13/$F$10</f>
-        <v>0.11425026999416077</v>
+        <f>F13/G13</f>
+        <v>542.70053763440853</v>
+      </c>
+      <c r="I13" s="1">
+        <v>542.70053763440853</v>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" ref="J13" si="3">I13-H13</f>
+        <v>0</v>
       </c>
       <c r="K13" s="4">
-        <f>1-K14</f>
-        <v>0.77</v>
-      </c>
-      <c r="L13" s="12">
+        <f t="shared" ref="K13:K16" si="4">IFERROR(J13/H13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <f t="shared" ref="L13:L14" si="5">H13/$H$10</f>
+        <v>0.19329003587100987</v>
+      </c>
+      <c r="M13" s="4">
+        <f>1-M14</f>
+        <v>0.8</v>
+      </c>
+      <c r="N13" s="12">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="M13" s="12">
+      <c r="O13" s="12">
         <v>0.08</v>
       </c>
-      <c r="P13" s="6"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="10"/>
-      <c r="U13" s="9"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="R13" s="6"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="10"/>
+      <c r="W13" s="9"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D14" s="15" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="1">
-        <v>1765</v>
-      </c>
-      <c r="G14" s="1">
-        <v>2072.9499999999998</v>
-      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
       <c r="H14" s="1">
-        <f>G14-F14</f>
-        <v>307.94999999999982</v>
-      </c>
-      <c r="I14" s="4">
-        <f t="shared" si="3"/>
-        <v>0.17447592067988657</v>
-      </c>
-      <c r="J14" s="4">
+        <v>2265</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2696</v>
+      </c>
+      <c r="J14" s="1">
+        <f>I14-H14</f>
+        <v>431</v>
+      </c>
+      <c r="K14" s="4">
         <f t="shared" si="4"/>
-        <v>0.67828308017896988</v>
-      </c>
-      <c r="K14" s="4">
-        <v>0.23</v>
-      </c>
-      <c r="L14" s="12">
+        <v>0.1902869757174393</v>
+      </c>
+      <c r="L14" s="4">
+        <f t="shared" si="5"/>
+        <v>0.8067099641289901</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N14" s="12">
         <v>0.1</v>
       </c>
-      <c r="M14" s="12">
+      <c r="O14" s="12">
         <v>0.307</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D15" s="15" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <f>G15-F15</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="4">
-        <f t="shared" ref="J15:J16" si="5">F15/$F$10</f>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <f>I15-H15</f>
         <v>0</v>
       </c>
       <c r="K15" s="4">
-        <v>0</v>
-      </c>
-      <c r="L15" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <f t="shared" ref="L15:L17" si="6">H15/$H$10</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="12">
         <v>3.2500000000000001E-2</v>
       </c>
-      <c r="M15" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="O15" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <f>G16-F16</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="4">
-        <f t="shared" si="5"/>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <f>I16-H16</f>
         <v>0</v>
       </c>
       <c r="K16" s="4">
-        <v>0</v>
-      </c>
-      <c r="L16" s="12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="12">
         <v>0.06</v>
       </c>
-      <c r="M16" s="12">
+      <c r="O16" s="12">
         <v>0.08</v>
       </c>
     </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D17" s="15" t="s">
         <v>29</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <f>G17-F17</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="4">
-        <f t="shared" ref="I17" si="6">IFERROR(H17/F17,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J17">
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <f>I17-H17</f>
         <v>0</v>
       </c>
       <c r="K17" s="4">
-        <v>0</v>
-      </c>
-      <c r="L17" s="12">
+        <f t="shared" ref="K17" si="7">IFERROR(J17/H17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="4">
+        <v>0</v>
+      </c>
+      <c r="N17" s="12">
         <v>0.13</v>
       </c>
-      <c r="M17" s="12">
+      <c r="O17" s="12">
         <v>0.08</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="H9:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
